--- a/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TESTING_PROCESS.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TESTING_PROCESS.xlsx
@@ -453,19 +453,19 @@
         <v>STLC bắt đầu bằng phân tích yêu cầu (Requirement Analysis) để xác định xem cái gì có thể test được (testable) và chuẩn bị các câu hỏi làm rõ nghiệp vụ.</v>
       </c>
       <c r="E2" t="str">
+        <v>Test Case Design — Thiết kế và viết chi tiết các kịch bản test case — giai đoạn thiết kế</v>
+      </c>
+      <c r="F2" t="str">
         <v>Requirement Analysis — Phân tích yêu cầu kiểm thử để xác định phạm vi và mục tiêu kiểm thử — giai đoạn phân tích</v>
       </c>
-      <c r="F2" t="str">
-        <v>Test Case Design — Thiết kế và viết chi tiết các kịch bản test case — giai đoạn thiết kế</v>
-      </c>
       <c r="G2" t="str">
+        <v>Test Closure — Tổng kết kết quả kiểm thử và ký biên bản nghiệm thu bàn giao — giai đoạn đóng test</v>
+      </c>
+      <c r="H2" t="str">
         <v>Test Execution — Tiến hành chạy thử nghiệm phần mềm và ghi nhận kết quả — giai đoạn thực thi</v>
       </c>
-      <c r="H2" t="str">
-        <v>Test Closure — Tổng kết kết quả kiểm thử và ký biên bản nghiệm thu bàn giao — giai đoạn đóng test</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Khi developer sửa xong bug, họ chuyển trạng thái bug sang Resolved (hoặc Ready for Test) để chỉ định cho QA kiểm tra lại (Retest).</v>
       </c>
       <c r="E3" t="str">
+        <v>Do Project Manager thiết lập khi họ quyết định không sửa lỗi đó trong dự án hiện tại — quản lý hoãn sửa</v>
+      </c>
+      <c r="F3" t="str">
         <v>Do Developer thiết lập khi họ đã sửa xong lỗi trong mã nguồn và sẵn sàng để QA kiểm tra lại — lập trình viên đã sửa xong</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v>Do người dùng cuối thiết lập khi họ đang chạy thử nghiệm hệ thống ở giai đoạn UAT — người dùng nghiệm thu</v>
+      </c>
+      <c r="H3" t="str">
         <v>Do QA thiết lập khi họ vừa mới phát hiện ra lỗi và nhập lên hệ thống — kiểm thử viên phát hiện</v>
       </c>
-      <c r="G3" t="str">
-        <v>Do Project Manager thiết lập khi họ quyết định không sửa lỗi đó trong dự án hiện tại — quản lý hoãn sửa</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Do người dùng cuối thiết lập khi họ đang chạy thử nghiệm hệ thống ở giai đoạn UAT — người dùng nghiệm thu</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Retesting (kiểm thử lại) tập trung chạy đúng kịch bản bị lỗi trước đó để xác nhận xem lỗi đó đã được sửa triệt để chưa. Khác với Regression testing (kiểm thử hồi quy).</v>
       </c>
       <c r="E4" t="str">
+        <v>Đo lường thời gian phản hồi của trang web khi có 100 người dùng truy cập — kiểm thử hiệu năng</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Thay đổi màu sắc của nút bấm trên giao diện theo thiết kế mới — cập nhật giao diện</v>
+      </c>
+      <c r="G4" t="str">
         <v>Xác nhận xem lỗi cụ thể đó đã thực sự được sửa thành công hay chưa — xác nhận sửa lỗi</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>Tìm kiếm các lỗi mới phát sinh ở các khu vực không liên quan khác của phần mềm — kiểm thử hồi quy</v>
       </c>
-      <c r="G4" t="str">
-        <v>Đo lường thời gian phản hồi của trang web khi có 100 người dùng truy cập — kiểm thử hiệu năng</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Thay đổi màu sắc của nút bấm trên giao diện theo thiết kế mới — cập nhật giao diện</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -546,10 +546,10 @@
         <v>Liệt kê chi tiết các bước nhập liệu cụ thể cho từng màn hình của ứng dụng — kịch bản chi tiết</v>
       </c>
       <c r="G5" t="str">
+        <v>Biên bản họp bàn giao sản phẩm giữa đội phát triển và khách hàng — biên bản bàn giao</v>
+      </c>
+      <c r="H5" t="str">
         <v>Ghi chép mã nguồn của các kịch bản kiểm thử tự động viết bằng ngôn ngữ Java — mã nguồn test</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Biên bản họp bàn giao sản phẩm giữa đội phát triển và khách hàng — biên bản bàn giao</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -569,19 +569,19 @@
         <v>Lỗi sập nguồn ngay khi mở app là lỗi Blocker vì nó ngăn cản hoàn toàn việc tiếp cận và test các tính năng khác của phần mềm.</v>
       </c>
       <c r="E6" t="str">
+        <v>Minor — lỗi hiển thị giao diện nhẹ không ảnh hưởng đến chức năng nghiệp vụ — lỗi giao diện nhẹ</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Trivial — lỗi viết sai chính tả trong phần tài liệu hướng dẫn sử dụng — lỗi chính tả tài liệu</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Major — lỗi lớn nhưng người dùng vẫn có cách khác để sử dụng tính năng — lỗi lớn có giải pháp thay thế</v>
+      </c>
+      <c r="H6" t="str">
         <v>Blocker / Critical — lỗi chặn đứng toàn bộ hoạt động kiểm thử các chức năng tiếp theo — lỗi chặn dòng</v>
       </c>
-      <c r="F6" t="str">
-        <v>Major — lỗi lớn nhưng người dùng vẫn có cách khác để sử dụng tính năng — lỗi lớn có giải pháp thay thế</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Minor — lỗi hiển thị giao diện nhẹ không ảnh hưởng đến chức năng nghiệp vụ — lỗi giao diện nhẹ</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Trivial — lỗi viết sai chính tả trong phần tài liệu hướng dẫn sử dụng — lỗi chính tả tài liệu</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Priority (Độ ưu tiên) thể hiện độ khẩn cấp cần sửa (do PO hoặc PM quyết định). Severity (Mức độ nghiêm trọng) thể hiện mức độ phá hủy chức năng phần mềm (do QA quyết định).</v>
       </c>
       <c r="E7" t="str">
-        <v>Mức độ khẩn cấp cần phải sửa lỗi đó trước hay sau từ góc nhìn kinh doanh/tiến độ dự án — mức độ khẩn cấp sửa lỗi</v>
+        <v>Số lượng dòng code mà lập trình viên cần viết để sửa xong lỗi đó — độ dài sửa code</v>
       </c>
       <c r="F7" t="str">
         <v>Mức độ tác động kỹ thuật của lỗi đó đối với kiến trúc hệ thống bên trong — tác động kỹ thuật</v>
       </c>
       <c r="G7" t="str">
-        <v>Số lượng dòng code mà lập trình viên cần viết để sửa xong lỗi đó — độ dài sửa code</v>
+        <v>Mức lương hàng tháng của lập trình viên chịu trách nhiệm sửa lỗi đó — chi phí sửa lỗi</v>
       </c>
       <c r="H7" t="str">
-        <v>Mức lương hàng tháng của lập trình viên chịu trách nhiệm sửa lỗi đó — chi phí sửa lỗi</v>
+        <v>Mức độ khẩn cấp cần phải sửa lỗi đó trước hay sau từ góc nhìn kinh doanh/tiến độ dự án — mức độ khẩn cấp sửa lỗi</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -633,10 +633,10 @@
         <v>Developer từ chối sửa lỗi vì cho rằng đó là tính năng thiết kế đúng — developer từ chối sửa</v>
       </c>
       <c r="G8" t="str">
+        <v>Khách hàng đồng ý nghiệm thu tính năng bất chấp lỗi vẫn đang tồn tại — nghiệm thu chấp nhận lỗi</v>
+      </c>
+      <c r="H8" t="str">
         <v>Project Manager quyết định hoãn việc sửa lỗi này sang dự án năm sau — hoãn sửa lỗi</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Khách hàng đồng ý nghiệm thu tính năng bất chấp lỗi vẫn đang tồn tại — nghiệm thu chấp nhận lỗi</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -656,10 +656,10 @@
         <v>Test Case Specification chứa các test cases chi tiết gồm: ID, Title, Pre-condition, Steps, Test Data, Expected Result, Actual Result, Status.</v>
       </c>
       <c r="E9" t="str">
+        <v>Mã nguồn Java/Python dùng để cấu hình tự động chạy CI/CD cho dự án — cấu hình CI/CD</v>
+      </c>
+      <c r="F9" t="str">
         <v>Danh sách các kịch bản kiểm thử chi tiết bao gồm điều kiện tiên quyết, các bước thực hiện, dữ liệu test và kết quả mong đợi — đặc tả kịch bản test</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Mã nguồn Java/Python dùng để cấu hình tự động chạy CI/CD cho dự án — cấu hình CI/CD</v>
       </c>
       <c r="G9" t="str">
         <v>Bản vẽ thiết kế giao diện đồ họa chi tiết của trang web bán hàng — bản vẽ thiết kế</v>
@@ -668,7 +668,7 @@
         <v>Báo cáo doanh số bán hàng hàng tháng của doanh nghiệp khách hàng — báo cáo doanh số</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>V-Model ánh xạ trực tiếp các mức test với các giai đoạn thiết kế: Unit Test đối chiếu với Detailed Design; Integration Test đối chiếu với High-level Design; System Test đối chiếu với SRS; Acceptance Test đối chiếu với Business Needs.</v>
       </c>
       <c r="E10" t="str">
+        <v>User Business Needs — Nhu cầu nghiệp vụ thực tế của người dùng cuối — nhu cầu nghiệp vụ</v>
+      </c>
+      <c r="F10" t="str">
         <v>Component Design / Detailed Design — Thiết kế chi tiết thành phần/mã nguồn — thiết kế chi tiết</v>
-      </c>
-      <c r="F10" t="str">
-        <v>System Architecture / High-Level Design — Thiết kế kiến trúc hệ thống cấp cao — thiết kế hệ thống</v>
       </c>
       <c r="G10" t="str">
         <v>Requirements Specification (SRS) — Tài liệu đặc tả yêu cầu phần mềm cấp cao — tài liệu yêu cầu</v>
       </c>
       <c r="H10" t="str">
-        <v>User Business Needs — Nhu cầu nghiệp vụ thực tế của người dùng cuối — nhu cầu nghiệp vụ</v>
+        <v>System Architecture / High-Level Design — Thiết kế kiến trúc hệ thống cấp cao — thiết kế hệ thống</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Bug Density (ví dụ: 2 bugs/1000 lines of code) giúp đánh giá chất lượng mã nguồn. Defect Leakage (ví dụ: 10% bugs bị khách hàng tìm thấy ở UAT) phản ánh trực tiếp hiệu quả và chất lượng của quy trình test của team QA.</v>
       </c>
       <c r="E11" t="str">
+        <v>Bug Density đo lường tốc độ phản hồi của trang web; Defect Leakage đo lường tốc độ rò rỉ bộ nhớ RAM — chỉ số hiệu năng phần cứng</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Bug Density do PM tính toán; Defect Leakage do QA Leader bắt buộc phải chịu trách nhiệm bồi thường tiền — trách nhiệm nhân sự</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Bug Density chỉ dùng cho kiểm thử tự động; Defect Leakage chỉ dùng cho kiểm thử thủ công — phân loại phương pháp test</v>
+      </c>
+      <c r="H11" t="str">
         <v>Bug Density tính bằng số lỗi chia cho kích thước phần mềm (ví dụ: KLOC); Defect Leakage tính bằng tỷ lệ lỗi bị bỏ sót trôi lên môi trường UAT/Production chia cho tổng số lỗi — lỗi trên kích thước vs lỗi bỏ sót lên môi trường sau</v>
       </c>
-      <c r="F11" t="str">
-        <v>Bug Density chỉ dùng cho kiểm thử tự động; Defect Leakage chỉ dùng cho kiểm thử thủ công — phân loại phương pháp test</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Bug Density do PM tính toán; Defect Leakage do QA Leader bắt buộc phải chịu trách nhiệm bồi thường tiền — trách nhiệm nhân sự</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Bug Density đo lường tốc độ phản hồi của trang web; Defect Leakage đo lường tốc độ rò rỉ bộ nhớ RAM — chỉ số hiệu năng phần cứng</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Một Bug Report tốt phải giúp dev tái hiện lại được lỗi (Reproducible). Các bước thực hiện rõ ràng, dữ liệu test cụ thể và bằng chứng (screenshot, video, console logs) là chìa khóa để dev định vị vùng code lỗi.</v>
       </c>
       <c r="E12" t="str">
-        <v>Steps to Reproduce (Các bước tái hiện), Expected Result (Kết quả mong đợi) và Actual Result (Kết quả thực tế xảy ra) kèm theo log/ảnh chụp màn hình — thông tin kỹ thuật tái hiện lỗi</v>
+        <v>Đoạn mã code sửa lỗi gợi ý viết bằng ngôn ngữ lập trình Java của QA — code sửa lỗi gợi ý</v>
       </c>
       <c r="F12" t="str">
         <v>Tên và mức lương hiện tại của kiểm thử viên đã tìm ra lỗi đó — thông tin nhân sự tìm lỗi</v>
       </c>
       <c r="G12" t="str">
-        <v>Đoạn mã code sửa lỗi gợi ý viết bằng ngôn ngữ lập trình Java của QA — code sửa lỗi gợi ý</v>
+        <v>Steps to Reproduce (Các bước tái hiện), Expected Result (Kết quả mong đợi) và Actual Result (Kết quả thực tế xảy ra) kèm theo log/ảnh chụp màn hình — thông tin kỹ thuật tái hiện lỗi</v>
       </c>
       <c r="H12" t="str">
         <v>Số lượng khách hàng tối đa sẽ bị ảnh hưởng bởi lỗi này trong tương lai — ước lượng tác động khách hàng</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -778,10 +778,10 @@
         <v>Xác định xem lập trình viên nào được phép vào và ra khỏi phòng máy chủ của dự án — kiểm soát ra vào vật lý</v>
       </c>
       <c r="G13" t="str">
+        <v>Định nghĩa mức chi phí tối thiểu và tối đa được phép chi tiêu cho công cụ kiểm thử tự động — kiểm soát chi phí công cụ</v>
+      </c>
+      <c r="H13" t="str">
         <v>Xác định số lượng test case tối đa được phép viết và xóa bỏ trong một ngày — giới hạn số lượng test case</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Định nghĩa mức chi phí tối thiểu và tối đa được phép chi tiêu cho công cụ kiểm thử tự động — kiểm soát chi phí công cụ</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Đây là trường hợp kinh điển: Lỗi không phá hủy tính năng (Severity Low) nhưng ảnh hưởng nặng đến thương hiệu/người dùng lớn (Priority High). Điều này chứng minh Severity và Priority không phải lúc nào cũng đi đôi với nhau.</v>
       </c>
       <c r="E14" t="str">
+        <v>Severity: Critical; Priority: High — lỗi làm hỏng toàn bộ tính năng thanh toán của ứng dụng di động — lỗi nghiêm trọng</v>
+      </c>
+      <c r="F14" t="str">
         <v>Severity: Low (Lỗi giao diện nhẹ không hỏng chức năng); Priority: High (Cần sửa gấp vì ảnh hưởng nghiêm trọng đến hình ảnh thương hiệu và trải nghiệm khách hàng VIP) — Severity thấp - Priority cao</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Severity: High (Sập hệ thống); Priority: Low (Không cần sửa trong vòng một năm tới) — Severity cao - Priority thấp</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Severity: Critical; Priority: High — lỗi làm hỏng toàn bộ tính năng thanh toán của ứng dụng di động — lỗi nghiêm trọng</v>
       </c>
       <c r="H14" t="str">
         <v>Severity: Low; Priority: Low — lỗi giao diện nhỏ ở màn hình ẩn sâu bên trong tài liệu hướng dẫn — lỗi nhỏ ít tương tác</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Trong Scrum, QA là một phần của Development Team. QA thực hiện phân tích yêu cầu ở buổi planning, viết test case ở các ngày đầu sprint, test liên tục (in-sprint testing) để đảm bảo User Story đạt DoD vào cuối sprint.</v>
       </c>
       <c r="E15" t="str">
+        <v>QA ngồi chơi trong 2 tuần đầu và chỉ bắt đầu làm việc khi Sprint đã kết thúc hoàn toàn — kiểm thử cuối kỳ</v>
+      </c>
+      <c r="F15" t="str">
+        <v>QA bắt buộc phải ngồi chung phòng và dùng chung máy tính với Product Owner khi chạy test — ngồi chung máy tính</v>
+      </c>
+      <c r="G15" t="str">
         <v>QA tham gia ngay từ đầu Sprint, viết test case dựa trên User Story/AC và thực hiện test liên tục ngay khi dev bàn giao từng phần tính năng — kiểm thử liên tục trong Sprint</v>
       </c>
-      <c r="F15" t="str">
-        <v>QA ngồi chơi trong 2 tuần đầu và chỉ bắt đầu làm việc khi Sprint đã kết thúc hoàn toàn — kiểm thử cuối kỳ</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>QA chỉ làm nhiệm vụ viết báo cáo lỗi, toàn bộ việc chạy test do lập trình viên tự thực hiện — lập trình viên tự test</v>
       </c>
-      <c r="H15" t="str">
-        <v>QA bắt buộc phải ngồi chung phòng và dùng chung máy tính với Product Owner khi chạy test — ngồi chung máy tính</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>RTM (Ma trận truy vết yêu cầu) liên kết: Yêu cầu nghiệp vụ -&gt; Test Case -&gt; Bug ID. RTM giúp QA kiểm soát xem có yêu cầu nào bị bỏ sót không có test case (thiếu coverage) hoặc có test case nào chạy fail mà chưa được log bug không.</v>
       </c>
       <c r="E16" t="str">
+        <v>Tính toán tổng số lỗi tối đa mà hệ thống có thể gặp phải trước khi sập máy chủ — dự báo lỗi hệ thống</v>
+      </c>
+      <c r="F16" t="str">
         <v>Ánh xạ các yêu cầu nghiệp vụ với các test case tương ứng để đảm bảo 100% yêu cầu đều được thiết kế kịch bản kiểm thử — bảo đảm độ bao phủ yêu cầu (Test Coverage)</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>Theo dõi thời gian đi làm và ra về hàng ngày của các lập trình viên trong công ty — chấm công nhân sự</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Tự động chạy các kịch bản kiểm thử tự động trên môi trường Jenkins CI/CD — chạy test tự động</v>
       </c>
-      <c r="H16" t="str">
-        <v>Tính toán tổng số lỗi tối đa mà hệ thống có thể gặp phải trước khi sập máy chủ — dự báo lỗi hệ thống</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Trạng thái Deferred nghĩa là lỗi được ghi nhận nhưng bị hoãn sửa (thường do độ ưu tiên thấp, sắp đến ngày release, hoặc sửa lỗi này có nguy cơ phá vỡ các tính năng khác lớn hơn).</v>
       </c>
       <c r="E17" t="str">
-        <v>Khi PO hoặc PM xác nhận lỗi có tồn tại nhưng quyết định hoãn sửa sang các bản release tiếp theo do không kịp tiến độ hoặc lỗi quá nhẹ — hoãn sửa lỗi có chủ đích</v>
+        <v>Khi hệ thống tự động sửa lỗi thành công mà không cần lập trình viên can thiệp — tự động sửa lỗi</v>
       </c>
       <c r="F17" t="str">
         <v>Khi Developer đã sửa xong lỗi và đang đợi QA chạy kiểm thử để đóng bug — chờ kiểm thử lại</v>
       </c>
       <c r="G17" t="str">
+        <v>Khi PO hoặc PM xác nhận lỗi có tồn tại nhưng quyết định hoãn sửa sang các bản release tiếp theo do không kịp tiến độ hoặc lỗi quá nhẹ — hoãn sửa lỗi có chủ đích</v>
+      </c>
+      <c r="H17" t="str">
         <v>Khi QA phát hiện ra lỗi nhưng tự ý xóa bỏ bản ghi lỗi đó ra khỏi hệ thống Jira — tự ý xóa lỗi</v>
       </c>
-      <c r="H17" t="str">
-        <v>Khi hệ thống tự động sửa lỗi thành công mà không cần lập trình viên can thiệp — tự động sửa lỗi</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Báo cáo tiến độ chạy test hàng ngày giúp PM và khách hàng biết được team test đã đi được bao xa (ví dụ: đã chạy 80% test cases, tỷ lệ pass đạt 90%, bị blocked 5% do môi trường lỗi).</v>
       </c>
       <c r="E18" t="str">
+        <v>Tổng chi phí bản quyền phần mềm đã mua cho công cụ Jira và Confluence — chi phí phần mềm</v>
+      </c>
+      <c r="F18" t="str">
         <v>Tỷ lệ phần trăm các test case ở trạng thái: Passed, Failed, Blocked, và Untested (Chưa chạy) — phân bổ trạng thái thực thi</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Số lượng dòng code Java đã viết thành công so với kế hoạch ban đầu — tiến độ viết code</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Tổng chi phí bản quyền phần mềm đã mua cho công cụ Jira và Confluence — chi phí phần mềm</v>
       </c>
       <c r="H18" t="str">
         <v>Số lượng nhân viên QA đã xin nghỉ phép trong quá trình dự án đang chạy test — nhân sự nghỉ phép</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -946,10 +946,10 @@
         <v>Race condition hoặc lỗi dưới mạng yếu rất khó tái hiện trên môi trường dev local vốn có mạng rất nhanh. QA không được đóng bug nhạy cảm này. Cần cung cấp các công cụ giả lập (Network Throttling trong DevTools) và log chi tiết để chứng minh lỗi có tồn tại thực tế.</v>
       </c>
       <c r="E19" t="str">
+        <v>Đồng ý đóng bug theo yêu cầu của dev vì nếu dev không tái hiện được thì lỗi không tồn tại thực tế — đóng bug thụ động</v>
+      </c>
+      <c r="F19" t="str">
         <v>Giữ nguyên bug ở trạng thái Open, cung cấp thêm thông tin log mạng chi tiết (Fiddler/Charles proxy logs, console error, latency simulated), mô tả chính xác cách giả lập mạng yếu để hỗ trợ dev định vị race condition — kiên trì cung cấp bằng chứng kỹ thuật</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Đồng ý đóng bug theo yêu cầu của dev vì nếu dev không tái hiện được thì lỗi không tồn tại thực tế — đóng bug thụ động</v>
       </c>
       <c r="G19" t="str">
         <v>Tự ý nhảy vào sửa code của hệ thống để sửa lỗi này giúp lập trình viên — lấn sân lập trình viên</v>
@@ -958,7 +958,7 @@
         <v>Gửi email khiếu nại trực tiếp lên ban giám đốc để kỷ luật lập trình viên đó vì thái độ làm việc kém — khiếu nại nhân sự</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Defect Leakage Rate đo lường tỷ lệ bug lọt lưới lên môi trường thực tế (production). Tỷ lệ này cao chứng tỏ quy trình kiểm thử của team QA chưa tốt, bỏ sót nhiều kịch bản biên hoặc môi trường test không đồng bộ với production.</v>
       </c>
       <c r="E20" t="str">
+        <v>$\text{Defect Leakage Rate} = (\text{Số bug bị Dev Reject} / \text{Tổng số bug đã báo cáo}) \cdot 100\%$; phản ánh độ chính xác khi báo cáo lỗi của QA — tỷ lệ bug bị reject</v>
+      </c>
+      <c r="F20" t="str">
         <v>$\text{Defect Leakage Rate} = (\text{Bugs tìm thấy ở Production} / (\text{Bugs tìm thấy ở Test} + \text{Bugs tìm thấy ở Production})) \cdot 100\%$; phản ánh hiệu quả bao phủ của bộ test case — tỷ lệ rò rỉ lỗi lên production</v>
       </c>
-      <c r="F20" t="str">
-        <v>$\text{Defect Leakage Rate} = (\text{Số bug bị Dev Reject} / \text{Tổng số bug đã báo cáo}) \cdot 100\%$; phản ánh độ chính xác khi báo cáo lỗi của QA — tỷ lệ bug bị reject</v>
-      </c>
       <c r="G20" t="str">
+        <v>$\text{Defect Leakage Rate} = (\text{Số test case chạy fail} / \text{Tổng số test case đã chạy}) \cdot 100\%$; phản ánh mức độ nghiêm trọng của phần mềm — tỷ lệ test case fail</v>
+      </c>
+      <c r="H20" t="str">
         <v>$\text{Defect Leakage Rate} = (\text{Số dòng code bị lỗi} / \text{Tổng số dòng code đã viết}) \cdot 100\%$; phản ánh chất lượng code của lập trình viên — mật độ lỗi code</v>
       </c>
-      <c r="H20" t="str">
-        <v>$\text{Defect Leakage Rate} = (\text{Số test case chạy fail} / \text{Tổng số test case đã chạy}) \cdot 100\%$; phản ánh mức độ nghiêm trọng của phần mềm — tỷ lệ test case fail</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1033,19 +1033,19 @@
         <v>Chất trọng tài nằm ở PO/BA. Vì họ là người nắm rõ kỳ vọng của người dùng và yêu cầu nghiệp vụ của sản phẩm. Nếu tài liệu SRS/User Story chưa rõ ràng, PO/BA sẽ đưa ra quyết định làm rõ (clarification).</v>
       </c>
       <c r="E22" t="str">
-        <v>BA hoặc Product Owner (PO) là người sở hữu yêu cầu nghiệp vụ sẽ đứng ra phân xử và đưa ra quyết định cuối cùng; nếu là bug thì dev phải sửa, nếu là tính năng mới thì PO sẽ đưa vào backlog — PO/BA phân xử dựa trên nghiệp vụ</v>
+        <v>Developer có quyền tối cao quyết định đóng bug ngay lập tức mà không cần sự đồng ý của bất kỳ ai — quyền lực thuộc về developer</v>
       </c>
       <c r="F22" t="str">
         <v>Hai bên tự thương lượng bằng cách bỏ phiếu bình chọn trong group chat, bên nào có nhiều người ủng hộ hơn sẽ thắng — bỏ phiếu bình chọn</v>
       </c>
       <c r="G22" t="str">
-        <v>Developer có quyền tối cao quyết định đóng bug ngay lập tức mà không cần sự đồng ý của bất kỳ ai — quyền lực thuộc về developer</v>
+        <v>BA hoặc Product Owner (PO) là người sở hữu yêu cầu nghiệp vụ sẽ đứng ra phân xử và đưa ra quyết định cuối cùng; nếu là bug thì dev phải sửa, nếu là tính năng mới thì PO sẽ đưa vào backlog — PO/BA phân xử dựa trên nghiệp vụ</v>
       </c>
       <c r="H22" t="str">
         <v>Project Manager đứng ra ép buộc QA phải đóng bug ngay lập tức để báo cáo tiến độ đẹp cho khách hàng — PM lạm quyền ép đóng bug</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>DoD là hợp đồng chất lượng của Scrum Team để đảm bảo phần tăng trưởng sản phẩm (Increment) thực sự sẵn sàng phát hành. AC là hợp đồng nghiệp vụ giữa PO và team để đảm bảo tính năng chạy đúng logic nghiệp vụ cụ thể của story đó.</v>
       </c>
       <c r="E23" t="str">
-        <v>DoD áp dụng chung cho mọi User Story trong Sprint (như: đã code, đã peer-review, đã test, không còn bug block, đã deploy); AC là điều kiện nghiệm thu riêng biệt cho các tính năng nghiệp vụ của từng story đó — tiêu chuẩn chất lượng chung vs điều kiện nghiệm thu riêng biệt</v>
+        <v>DoD chỉ áp dụng cho mã nguồn Backend; còn AC chỉ áp dụng cho giao diện người dùng Frontend — phân loại theo layer công nghệ</v>
       </c>
       <c r="F23" t="str">
         <v>DoD do khách hàng phê duyệt; còn AC do lập trình viên tự kiểm thử và xác nhận hoàn thành — phân biệt chủ thể phê duyệt</v>
       </c>
       <c r="G23" t="str">
-        <v>DoD chỉ áp dụng cho mã nguồn Backend; còn AC chỉ áp dụng cho giao diện người dùng Frontend — phân loại theo layer công nghệ</v>
+        <v>DoD luôn được thay đổi tự do hàng ngày; còn AC không bao giờ được phép chỉnh sửa sau khi đã chốt — tính ổn định chỉ số</v>
       </c>
       <c r="H23" t="str">
-        <v>DoD luôn được thay đổi tự do hàng ngày; còn AC không bao giờ được phép chỉnh sửa sau khi đã chốt — tính ổn định chỉ số</v>
+        <v>DoD áp dụng chung cho mọi User Story trong Sprint (như: đã code, đã peer-review, đã test, không còn bug block, đã deploy); AC là điều kiện nghiệm thu riêng biệt cho các tính năng nghiệp vụ của từng story đó — tiêu chuẩn chất lượng chung vs điều kiện nghiệm thu riêng biệt</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Tích hợp bên thứ ba (như cổng thanh toán, hệ thống eKYC) luôn là rủi ro lớn nhất cho môi trường test (Sandboxes của đối tác thường bị sập hoặc giới hạn dữ liệu). Sử dụng Mock Server giúp QA hoàn toàn chủ động giả lập các kịch bản thành công và đặc biệt là các kịch bản lỗi biên của đối tác để test hệ thống của mình.</v>
       </c>
       <c r="E24" t="str">
+        <v>Rủi ro: Máy chủ của bệnh viện bị mất điện; Giải pháp: Yêu cầu bệnh viện mua thêm 10 chiếc máy phát điện dự phòng — can thiệp hạ tầng vật lý đối tác</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Rủi ro: Khách hàng không biết cách sử dụng ứng dụng di động; Giải pháp: QA tự đi viết toàn bộ tài liệu hướng dẫn sử dụng thay BA — đùn đẩy công việc của BA</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Rủi ro: Lập trình viên viết code sai cú pháp; Giải pháp: Yêu cầu lập trình viên phải đổi sang sử dụng máy tính chạy hệ điều hành MacOS — giải pháp phần cứng không liên quan</v>
+      </c>
+      <c r="H24" t="str">
         <v>Rủi ro: Môi trường test của bên thứ ba không ổn định hoặc không có sẵn dữ liệu test thực tế; Giải pháp: Yêu cầu team dev xây dựng hệ thống giả lập phản hồi (Mock Server/Stubs) để giả lập hành vi của các bên thứ ba — quản lý rủi ro môi trường liên kết</v>
       </c>
-      <c r="F24" t="str">
-        <v>Rủi ro: Lập trình viên viết code sai cú pháp; Giải pháp: Yêu cầu lập trình viên phải đổi sang sử dụng máy tính chạy hệ điều hành MacOS — giải pháp phần cứng không liên quan</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Rủi ro: Khách hàng không biết cách sử dụng ứng dụng di động; Giải pháp: QA tự đi viết toàn bộ tài liệu hướng dẫn sử dụng thay BA — đùn đẩy công việc của BA</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Rủi ro: Máy chủ của bệnh viện bị mất điện; Giải pháp: Yêu cầu bệnh viện mua thêm 10 chiếc máy phát điện dự phòng — can thiệp hạ tầng vật lý đối tác</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Defect Rejection Rate cao gây lãng phí tài nguyên của dự án (dev mất công kiểm tra rồi reject, QA mất công log). Nó phản ánh QA đang hấp tấp log bug mà chưa đọc kỹ tài liệu đặc tả, hoặc do tài liệu quá mơ hồ khiến các bên hiểu lệch pha nhau.</v>
       </c>
       <c r="E25" t="str">
+        <v>Tỷ lệ giữa số dòng code bị xóa bỏ chia cho tổng số dòng code đã viết; tỷ lệ cao cảnh báo code chất lượng kém — chất lượng mã nguồn</v>
+      </c>
+      <c r="F25" t="str">
         <v>Tỷ lệ giữa số bug bị dev reject (do hiểu sai spec, trùng lặp, hoặc không phải lỗi) chia cho tổng số bug đã báo cáo; tỷ lệ cao cảnh báo QA đang không nắm vững nghiệp vụ (SRS/AC) hoặc viết bug report mơ hồ — chất lượng báo cáo lỗi và hiểu nghiệp vụ của QA</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Tỷ lệ giữa số bug được sửa thành công chia cho tổng số bug đang mở; tỷ lệ cao cảnh báo dev đang làm việc quá tải — năng suất sửa bug của dev</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Tỷ lệ giữa số dòng code bị xóa bỏ chia cho tổng số dòng code đã viết; tỷ lệ cao cảnh báo code chất lượng kém — chất lượng mã nguồn</v>
       </c>
       <c r="H25" t="str">
         <v>Tỷ lệ giữa số test case bị viết sai cú pháp chia cho tổng số test case đã chạy; tỷ lệ cao cảnh báo năng lực viết test của QA kém — năng lực viết test case</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Hệ thống ERP lớn có hàng nghìn test cases. Chạy tay hàng tuần là không thể. Tự động hóa bộ test lõi (Regression Suite) giúp chạy nhanh qua đêm. Kết hợp Impact Analysis từ code change giúp QA khoanh vùng (scope) các khu vực có nguy cơ bị ảnh hưởng (side effects) để test tay bổ sung.</v>
       </c>
       <c r="E26" t="str">
+        <v>Yêu cầu toàn bộ các lập trình viên tự chạy test hồi quy trên máy của mình trước khi release — đùn đẩy trách nhiệm</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Bỏ qua hoàn toàn việc kiểm thử hồi quy, chỉ kiểm tra các tính năng mới viết thêm trong tuần đó — bỏ qua test hồi quy rủi ro cao</v>
+      </c>
+      <c r="G26" t="str">
         <v>Xây dựng bộ test case hồi quy cốt lõi (Regression Suite), tự động hóa các kịch bản test ổn định này bằng script test (Automation), và áp dụng phân tích tác động (Impact Analysis) để chỉ chạy thêm test case thủ công ở các vùng code bị ảnh hưởng trực tiếp bởi thay đổi — kết hợp Automation và phân tích tác động</v>
       </c>
-      <c r="F26" t="str">
+      <c r="H26" t="str">
         <v>Chạy lại toàn bộ 100% các test case thủ công có sẵn trong file Excel một cách tuần tự từ đầu đến cuối hàng tuần — chạy test thủ công toàn diện nặng nề</v>
       </c>
-      <c r="G26" t="str">
-        <v>Bỏ qua hoàn toàn việc kiểm thử hồi quy, chỉ kiểm tra các tính năng mới viết thêm trong tuần đó — bỏ qua test hồi quy rủi ro cao</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Yêu cầu toàn bộ các lập trình viên tự chạy test hồi quy trên máy của mình trước khi release — đùn đẩy trách nhiệm</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
